--- a/data/trans_orig/IP24_R_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>10190</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>779</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12597</t>
+          <t>14319</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>51436</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>45580</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>54722</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,23%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>81,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,12%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>52088</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>47730</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>53956</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,29%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56796</t>
+          <t>44118</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50769</t>
+          <t>40355</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59604</t>
+          <t>45979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>108883</t>
+          <t>95554</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103147</t>
+          <t>88209</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112722</t>
+          <t>99207</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>55770</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>55770</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>55770</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61067</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61067</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61067</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>115744</t>
+          <t>102528</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>115744</t>
+          <t>102528</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115744</t>
+          <t>102528</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>55442</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>44532</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>70291</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,7%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>33906</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>24161</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>46006</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,04%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>56484</t>
+          <t>32120</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45015</t>
+          <t>24551</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71541</t>
+          <t>41120</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>90390</t>
+          <t>87562</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73775</t>
+          <t>73251</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>105001</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>418242</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>403393</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>429152</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,3%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,16%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>587</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>424277</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>412177</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>434022</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>92,6%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,96%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>457563</t>
+          <t>398171</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>442506</t>
+          <t>389171</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>469032</t>
+          <t>405740</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>881841</t>
+          <t>816413</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>862130</t>
+          <t>798974</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>898456</t>
+          <t>830724</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>473684</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>473684</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>473684</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>639</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>458183</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>458183</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>458183</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514047</t>
+          <t>430291</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514047</t>
+          <t>430291</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514047</t>
+          <t>430291</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>972231</t>
+          <t>903975</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>972231</t>
+          <t>903975</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>972231</t>
+          <t>903975</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34544</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26337</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>45865</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>27,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19351</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13424</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26586</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,94%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,98%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>36035</t>
+          <t>20248</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27107</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46349</t>
+          <t>28203</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>55386</t>
+          <t>54792</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44608</t>
+          <t>44279</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67742</t>
+          <t>67333</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>133231</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>121910</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>141438</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79,41%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>72,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>197</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>130200</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>122965</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>136127</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>87,06%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,22%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>91,02%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>146548</t>
+          <t>129728</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136234</t>
+          <t>121773</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155476</t>
+          <t>135534</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>276748</t>
+          <t>262959</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264392</t>
+          <t>250418</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>287526</t>
+          <t>273472</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,06%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167775</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167775</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167775</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182583</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182583</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182583</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332134</t>
+          <t>317751</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332134</t>
+          <t>317751</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332134</t>
+          <t>317751</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>94319</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>79290</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>113187</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,23%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>55847</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>45001</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>71429</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,78%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>96789</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81121</t>
+          <t>45317</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114773</t>
+          <t>67697</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>152636</t>
+          <t>149328</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>130717</t>
+          <t>130896</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>173814</t>
+          <t>172229</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>602909</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>584041</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>617938</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,47%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,77%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,63%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>849</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>606565</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>590983</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>617411</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>91,57%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>660908</t>
+          <t>572017</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>642924</t>
+          <t>559328</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>676576</t>
+          <t>581708</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1267473</t>
+          <t>1174926</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1246295</t>
+          <t>1152025</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1289392</t>
+          <t>1193358</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>938</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>662412</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>662412</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>662412</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627025</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627025</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627025</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1420109</t>
+          <t>1324254</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1420109</t>
+          <t>1324254</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1420109</t>
+          <t>1324254</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
